--- a/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemDropTable.xlsx
+++ b/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemDropTable.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="EnemyDropRules" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="RarityWeights" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="ItemKindWeights" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EnemyDropRules" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RarityWeights" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ItemKindWeights" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ComboBox" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -509,6 +510,11 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="A3:A200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="잘못된 값" error="목록에 없는 값입니다. 드롭다운에서 선택해주세요." type="list">
+      <formula1>=ComboBox!$A$2:$A$6</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -862,6 +868,14 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="2">
+    <dataValidation sqref="A3:A200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="잘못된 값" error="목록에 없는 값입니다. 드롭다운에서 선택해주세요." type="list">
+      <formula1>=ComboBox!$A$2:$A$6</formula1>
+    </dataValidation>
+    <dataValidation sqref="B3:B200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="잘못된 값" error="목록에 없는 값입니다. 드롭다운에서 선택해주세요." type="list">
+      <formula1>=ComboBox!$B$2:$B$6</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -954,6 +968,134 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="A3:A200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="잘못된 값" error="목록에 없는 값입니다. 드롭다운에서 선택해주세요." type="list">
+      <formula1>=ComboBox!$C$2:$C$7</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>enemyGrade</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>rarity</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>itemKind</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Weapon</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Advanced</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Advanced</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Helmet</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Chest</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Boss</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Unique</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Boots</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Hidden</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Legendary</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Potion</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Relic</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>